--- a/Team-Data/2007-08/3-11-2007-08.xlsx
+++ b/Team-Data/2007-08/3-11-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>-3</v>
       </c>
       <c r="AD2" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AE2" t="n">
         <v>19</v>
@@ -784,7 +851,7 @@
         <v>4</v>
       </c>
       <c r="AS2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT2" t="n">
         <v>12</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-11-2007-08</t>
+          <t>2008-03-11</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>10.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -936,7 +1003,7 @@
         <v>23</v>
       </c>
       <c r="AI3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AJ3" t="n">
         <v>30</v>
@@ -984,13 +1051,13 @@
         <v>19</v>
       </c>
       <c r="AY3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ3" t="n">
         <v>25</v>
       </c>
       <c r="BA3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB3" t="n">
         <v>9</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-11-2007-08</t>
+          <t>2008-03-11</t>
         </is>
       </c>
     </row>
@@ -1103,19 +1170,19 @@
         <v>-4.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AE4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF4" t="n">
         <v>22</v>
       </c>
       <c r="AG4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI4" t="n">
         <v>23</v>
@@ -1127,7 +1194,7 @@
         <v>20</v>
       </c>
       <c r="AL4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM4" t="n">
         <v>15</v>
@@ -1136,7 +1203,7 @@
         <v>14</v>
       </c>
       <c r="AO4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP4" t="n">
         <v>11</v>
@@ -1148,22 +1215,22 @@
         <v>17</v>
       </c>
       <c r="AS4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU4" t="n">
         <v>18</v>
       </c>
       <c r="AV4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW4" t="n">
         <v>13</v>
       </c>
       <c r="AX4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY4" t="n">
         <v>30</v>
@@ -1175,7 +1242,7 @@
         <v>15</v>
       </c>
       <c r="BB4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BC4" t="n">
         <v>22</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-11-2007-08</t>
+          <t>2008-03-11</t>
         </is>
       </c>
     </row>
@@ -1207,61 +1274,61 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F5" t="n">
         <v>38</v>
       </c>
       <c r="G5" t="n">
-        <v>0.406</v>
+        <v>0.397</v>
       </c>
       <c r="H5" t="n">
         <v>48.4</v>
       </c>
       <c r="I5" t="n">
-        <v>36.1</v>
+        <v>36</v>
       </c>
       <c r="J5" t="n">
-        <v>84.3</v>
+        <v>84.2</v>
       </c>
       <c r="K5" t="n">
-        <v>0.429</v>
+        <v>0.428</v>
       </c>
       <c r="L5" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="M5" t="n">
         <v>15.8</v>
       </c>
       <c r="N5" t="n">
-        <v>0.353</v>
+        <v>0.351</v>
       </c>
       <c r="O5" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="P5" t="n">
         <v>25</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.745</v>
+        <v>0.746</v>
       </c>
       <c r="R5" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="S5" t="n">
         <v>30.2</v>
       </c>
       <c r="T5" t="n">
-        <v>43.7</v>
+        <v>43.6</v>
       </c>
       <c r="U5" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="V5" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="W5" t="n">
         <v>7.7</v>
@@ -1273,34 +1340,34 @@
         <v>5.8</v>
       </c>
       <c r="Z5" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="AA5" t="n">
         <v>21.7</v>
       </c>
-      <c r="AA5" t="n">
-        <v>21.6</v>
-      </c>
       <c r="AB5" t="n">
-        <v>96.5</v>
+        <v>96.3</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2.5</v>
+        <v>-2.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AE5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AF5" t="n">
         <v>20</v>
       </c>
       <c r="AG5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AI5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ5" t="n">
         <v>5</v>
@@ -1315,13 +1382,13 @@
         <v>23</v>
       </c>
       <c r="AN5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP5" t="n">
         <v>16</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>17</v>
       </c>
       <c r="AQ5" t="n">
         <v>19</v>
@@ -1330,19 +1397,19 @@
         <v>1</v>
       </c>
       <c r="AS5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AT5" t="n">
         <v>6</v>
       </c>
       <c r="AU5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AV5" t="n">
         <v>15</v>
       </c>
       <c r="AW5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX5" t="n">
         <v>9</v>
@@ -1354,10 +1421,10 @@
         <v>21</v>
       </c>
       <c r="BA5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BB5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC5" t="n">
         <v>20</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-11-2007-08</t>
+          <t>2008-03-11</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>-0.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE6" t="n">
         <v>12</v>
@@ -1482,10 +1549,10 @@
         <v>4</v>
       </c>
       <c r="AI6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AK6" t="n">
         <v>26</v>
@@ -1494,7 +1561,7 @@
         <v>12</v>
       </c>
       <c r="AM6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AN6" t="n">
         <v>13</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-11-2007-08</t>
+          <t>2008-03-11</t>
         </is>
       </c>
     </row>
@@ -1649,19 +1716,19 @@
         <v>4.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF7" t="n">
         <v>9</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>8</v>
       </c>
       <c r="AG7" t="n">
         <v>9</v>
       </c>
       <c r="AH7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI7" t="n">
         <v>17</v>
@@ -1679,7 +1746,7 @@
         <v>20</v>
       </c>
       <c r="AN7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO7" t="n">
         <v>8</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-11-2007-08</t>
+          <t>2008-03-11</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>2.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AE8" t="n">
         <v>12</v>
@@ -1843,7 +1910,7 @@
         <v>12</v>
       </c>
       <c r="AH8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI8" t="n">
         <v>5</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-11-2007-08</t>
+          <t>2008-03-11</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>7.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -2025,7 +2092,7 @@
         <v>2</v>
       </c>
       <c r="AH9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI9" t="n">
         <v>16</v>
@@ -2043,7 +2110,7 @@
         <v>22</v>
       </c>
       <c r="AN9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO9" t="n">
         <v>12</v>
@@ -2076,7 +2143,7 @@
         <v>5</v>
       </c>
       <c r="AY9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AZ9" t="n">
         <v>16</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-11-2007-08</t>
+          <t>2008-03-11</t>
         </is>
       </c>
     </row>
@@ -2195,13 +2262,13 @@
         <v>3.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AE10" t="n">
         <v>11</v>
       </c>
       <c r="AF10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG10" t="n">
         <v>11</v>
@@ -2210,7 +2277,7 @@
         <v>19</v>
       </c>
       <c r="AI10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ10" t="n">
         <v>1</v>
@@ -2225,7 +2292,7 @@
         <v>1</v>
       </c>
       <c r="AN10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO10" t="n">
         <v>14</v>
@@ -2240,7 +2307,7 @@
         <v>7</v>
       </c>
       <c r="AS10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT10" t="n">
         <v>11</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-11-2007-08</t>
+          <t>2008-03-11</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>5.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AE11" t="n">
         <v>5</v>
@@ -2416,7 +2483,7 @@
         <v>27</v>
       </c>
       <c r="AQ11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AR11" t="n">
         <v>10</v>
@@ -2443,7 +2510,7 @@
         <v>11</v>
       </c>
       <c r="AZ11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA11" t="n">
         <v>27</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-11-2007-08</t>
+          <t>2008-03-11</t>
         </is>
       </c>
     </row>
@@ -2481,25 +2548,25 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F12" t="n">
         <v>39</v>
       </c>
       <c r="G12" t="n">
-        <v>0.391</v>
+        <v>0.381</v>
       </c>
       <c r="H12" t="n">
         <v>48.2</v>
       </c>
       <c r="I12" t="n">
-        <v>37.7</v>
+        <v>37.6</v>
       </c>
       <c r="J12" t="n">
-        <v>85.5</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="K12" t="n">
         <v>0.441</v>
@@ -2511,25 +2578,25 @@
         <v>24.4</v>
       </c>
       <c r="N12" t="n">
-        <v>0.367</v>
+        <v>0.368</v>
       </c>
       <c r="O12" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="P12" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.77</v>
+        <v>0.769</v>
       </c>
       <c r="R12" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="S12" t="n">
         <v>32.1</v>
       </c>
       <c r="T12" t="n">
-        <v>43.4</v>
+        <v>43.3</v>
       </c>
       <c r="U12" t="n">
         <v>22.7</v>
@@ -2538,28 +2605,28 @@
         <v>15.5</v>
       </c>
       <c r="W12" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X12" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="AA12" t="n">
         <v>21.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>103</v>
+        <v>102.9</v>
       </c>
       <c r="AC12" t="n">
-        <v>-2.4</v>
+        <v>-2.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AE12" t="n">
         <v>22</v>
@@ -2580,7 +2647,7 @@
         <v>2</v>
       </c>
       <c r="AK12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL12" t="n">
         <v>3</v>
@@ -2592,7 +2659,7 @@
         <v>11</v>
       </c>
       <c r="AO12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP12" t="n">
         <v>21</v>
@@ -2610,7 +2677,7 @@
         <v>7</v>
       </c>
       <c r="AU12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV12" t="n">
         <v>27</v>
@@ -2619,7 +2686,7 @@
         <v>11</v>
       </c>
       <c r="AX12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY12" t="n">
         <v>22</v>
@@ -2628,13 +2695,13 @@
         <v>29</v>
       </c>
       <c r="BA12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BB12" t="n">
         <v>7</v>
       </c>
       <c r="BC12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-11-2007-08</t>
+          <t>2008-03-11</t>
         </is>
       </c>
     </row>
@@ -2741,13 +2808,13 @@
         <v>-5.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AE13" t="n">
         <v>25</v>
       </c>
       <c r="AF13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG13" t="n">
         <v>25</v>
@@ -2804,7 +2871,7 @@
         <v>14</v>
       </c>
       <c r="AY13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ13" t="n">
         <v>19</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-11-2007-08</t>
+          <t>2008-03-11</t>
         </is>
       </c>
     </row>
@@ -2845,22 +2912,22 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E14" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F14" t="n">
         <v>19</v>
       </c>
       <c r="G14" t="n">
-        <v>0.703</v>
+        <v>0.698</v>
       </c>
       <c r="H14" t="n">
         <v>48.2</v>
       </c>
       <c r="I14" t="n">
-        <v>39.6</v>
+        <v>39.5</v>
       </c>
       <c r="J14" t="n">
         <v>82.59999999999999</v>
@@ -2869,19 +2936,19 @@
         <v>0.479</v>
       </c>
       <c r="L14" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="M14" t="n">
-        <v>20.3</v>
+        <v>20.1</v>
       </c>
       <c r="N14" t="n">
-        <v>0.375</v>
+        <v>0.373</v>
       </c>
       <c r="O14" t="n">
-        <v>21.5</v>
+        <v>21.7</v>
       </c>
       <c r="P14" t="n">
-        <v>28.2</v>
+        <v>28.4</v>
       </c>
       <c r="Q14" t="n">
         <v>0.762</v>
@@ -2890,16 +2957,16 @@
         <v>10.8</v>
       </c>
       <c r="S14" t="n">
-        <v>33.4</v>
+        <v>33.5</v>
       </c>
       <c r="T14" t="n">
-        <v>44.1</v>
+        <v>44.3</v>
       </c>
       <c r="U14" t="n">
-        <v>24</v>
+        <v>23.8</v>
       </c>
       <c r="V14" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W14" t="n">
         <v>8.199999999999999</v>
@@ -2911,19 +2978,19 @@
         <v>4.7</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AA14" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="AB14" t="n">
-        <v>108.3</v>
+        <v>108.2</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
@@ -2935,7 +3002,7 @@
         <v>3</v>
       </c>
       <c r="AH14" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI14" t="n">
         <v>4</v>
@@ -2947,16 +3014,16 @@
         <v>3</v>
       </c>
       <c r="AL14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AM14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AN14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AO14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AP14" t="n">
         <v>4</v>
@@ -2977,7 +3044,7 @@
         <v>3</v>
       </c>
       <c r="AV14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW14" t="n">
         <v>6</v>
@@ -2989,10 +3056,10 @@
         <v>14</v>
       </c>
       <c r="AZ14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB14" t="n">
         <v>3</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-11-2007-08</t>
+          <t>2008-03-11</t>
         </is>
       </c>
     </row>
@@ -3027,16 +3094,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E15" t="n">
         <v>15</v>
       </c>
       <c r="F15" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G15" t="n">
-        <v>0.238</v>
+        <v>0.242</v>
       </c>
       <c r="H15" t="n">
         <v>48.3</v>
@@ -3045,43 +3112,43 @@
         <v>36.8</v>
       </c>
       <c r="J15" t="n">
-        <v>81.40000000000001</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>0.452</v>
+        <v>0.453</v>
       </c>
       <c r="L15" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="M15" t="n">
         <v>21.3</v>
       </c>
       <c r="N15" t="n">
-        <v>0.353</v>
+        <v>0.354</v>
       </c>
       <c r="O15" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="P15" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.735</v>
+        <v>0.734</v>
       </c>
       <c r="R15" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="S15" t="n">
         <v>30.9</v>
       </c>
       <c r="T15" t="n">
-        <v>41.1</v>
+        <v>41.2</v>
       </c>
       <c r="U15" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="V15" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="W15" t="n">
         <v>6.1</v>
@@ -3096,16 +3163,16 @@
         <v>19.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>99.5</v>
+        <v>99.3</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.7</v>
+        <v>-6.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="AE15" t="n">
         <v>28</v>
@@ -3117,7 +3184,7 @@
         <v>28</v>
       </c>
       <c r="AH15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI15" t="n">
         <v>13</v>
@@ -3129,7 +3196,7 @@
         <v>17</v>
       </c>
       <c r="AL15" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AM15" t="n">
         <v>5</v>
@@ -3150,7 +3217,7 @@
         <v>23</v>
       </c>
       <c r="AS15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT15" t="n">
         <v>20</v>
@@ -3165,10 +3232,10 @@
         <v>27</v>
       </c>
       <c r="AX15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ15" t="n">
         <v>3</v>
@@ -3180,7 +3247,7 @@
         <v>13</v>
       </c>
       <c r="BC15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-11-2007-08</t>
+          <t>2008-03-11</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>-7.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AE16" t="n">
         <v>30</v>
@@ -3347,7 +3414,7 @@
         <v>18</v>
       </c>
       <c r="AX16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY16" t="n">
         <v>4</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-11-2007-08</t>
+          <t>2008-03-11</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E17" t="n">
         <v>23</v>
       </c>
       <c r="F17" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G17" t="n">
-        <v>0.359</v>
+        <v>0.365</v>
       </c>
       <c r="H17" t="n">
         <v>48.3</v>
@@ -3409,7 +3476,7 @@
         <v>36.5</v>
       </c>
       <c r="J17" t="n">
-        <v>81.40000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="K17" t="n">
         <v>0.449</v>
@@ -3418,10 +3485,10 @@
         <v>5.5</v>
       </c>
       <c r="M17" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0.339</v>
+        <v>0.34</v>
       </c>
       <c r="O17" t="n">
         <v>17.5</v>
@@ -3433,19 +3500,19 @@
         <v>0.742</v>
       </c>
       <c r="R17" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="S17" t="n">
         <v>28.5</v>
       </c>
       <c r="T17" t="n">
-        <v>40.9</v>
+        <v>40.8</v>
       </c>
       <c r="U17" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="V17" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="W17" t="n">
         <v>6.5</v>
@@ -3454,7 +3521,7 @@
         <v>4.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Z17" t="n">
         <v>21.4</v>
@@ -3469,7 +3536,7 @@
         <v>-6.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AE17" t="n">
         <v>24</v>
@@ -3499,7 +3566,7 @@
         <v>21</v>
       </c>
       <c r="AN17" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AO17" t="n">
         <v>25</v>
@@ -3517,7 +3584,7 @@
         <v>30</v>
       </c>
       <c r="AT17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AU17" t="n">
         <v>19</v>
@@ -3526,19 +3593,19 @@
         <v>13</v>
       </c>
       <c r="AW17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ17" t="n">
         <v>17</v>
       </c>
       <c r="BA17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BB17" t="n">
         <v>24</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-11-2007-08</t>
+          <t>2008-03-11</t>
         </is>
       </c>
     </row>
@@ -3573,64 +3640,64 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E18" t="n">
         <v>14</v>
       </c>
       <c r="F18" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G18" t="n">
-        <v>0.222</v>
+        <v>0.226</v>
       </c>
       <c r="H18" t="n">
         <v>48.1</v>
       </c>
       <c r="I18" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J18" t="n">
         <v>82.90000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>0.444</v>
+        <v>0.443</v>
       </c>
       <c r="L18" t="n">
         <v>5.3</v>
       </c>
       <c r="M18" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="N18" t="n">
-        <v>0.34</v>
+        <v>0.338</v>
       </c>
       <c r="O18" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="P18" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.725</v>
+        <v>0.724</v>
       </c>
       <c r="R18" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="S18" t="n">
         <v>29.4</v>
       </c>
       <c r="T18" t="n">
-        <v>41.4</v>
+        <v>41.5</v>
       </c>
       <c r="U18" t="n">
         <v>19.5</v>
       </c>
       <c r="V18" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W18" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="X18" t="n">
         <v>3.7</v>
@@ -3642,16 +3709,16 @@
         <v>23.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>17.5</v>
+        <v>17.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>93.7</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AC18" t="n">
         <v>-7.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="AE18" t="n">
         <v>29</v>
@@ -3681,7 +3748,7 @@
         <v>24</v>
       </c>
       <c r="AN18" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AO18" t="n">
         <v>30</v>
@@ -3690,16 +3757,16 @@
         <v>29</v>
       </c>
       <c r="AQ18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AR18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AS18" t="n">
         <v>27</v>
       </c>
       <c r="AT18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU18" t="n">
         <v>26</v>
@@ -3708,7 +3775,7 @@
         <v>22</v>
       </c>
       <c r="AW18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX18" t="n">
         <v>29</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-11-2007-08</t>
+          <t>2008-03-11</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-5.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE19" t="n">
         <v>19</v>
@@ -3845,7 +3912,7 @@
         <v>20</v>
       </c>
       <c r="AH19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI19" t="n">
         <v>30</v>
@@ -3863,7 +3930,7 @@
         <v>18</v>
       </c>
       <c r="AN19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO19" t="n">
         <v>10</v>
@@ -3878,7 +3945,7 @@
         <v>15</v>
       </c>
       <c r="AS19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT19" t="n">
         <v>9</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-11-2007-08</t>
+          <t>2008-03-11</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>5</v>
       </c>
       <c r="AD20" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AE20" t="n">
         <v>6</v>
@@ -4042,7 +4109,7 @@
         <v>5</v>
       </c>
       <c r="AM20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AN20" t="n">
         <v>2</v>
@@ -4057,7 +4124,7 @@
         <v>8</v>
       </c>
       <c r="AR20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS20" t="n">
         <v>14</v>
@@ -4066,7 +4133,7 @@
         <v>10</v>
       </c>
       <c r="AU20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV20" t="n">
         <v>3</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-11-2007-08</t>
+          <t>2008-03-11</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-6.7</v>
       </c>
       <c r="AD21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE21" t="n">
         <v>26</v>
@@ -4224,7 +4291,7 @@
         <v>20</v>
       </c>
       <c r="AM21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AN21" t="n">
         <v>28</v>
@@ -4239,7 +4306,7 @@
         <v>22</v>
       </c>
       <c r="AR21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS21" t="n">
         <v>23</v>
@@ -4272,7 +4339,7 @@
         <v>26</v>
       </c>
       <c r="BC21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-11-2007-08</t>
+          <t>2008-03-11</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4449,7 @@
         <v>1</v>
       </c>
       <c r="AE22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF22" t="n">
         <v>11</v>
@@ -4454,7 +4521,7 @@
         <v>6</v>
       </c>
       <c r="BC22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-11-2007-08</t>
+          <t>2008-03-11</t>
         </is>
       </c>
     </row>
@@ -4561,10 +4628,10 @@
         <v>0.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF23" t="n">
         <v>17</v>
@@ -4573,7 +4640,7 @@
         <v>17</v>
       </c>
       <c r="AH23" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AI23" t="n">
         <v>10</v>
@@ -4627,10 +4694,10 @@
         <v>15</v>
       </c>
       <c r="AZ23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB23" t="n">
         <v>21</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-11-2007-08</t>
+          <t>2008-03-11</t>
         </is>
       </c>
     </row>
@@ -4665,64 +4732,64 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E24" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F24" t="n">
         <v>22</v>
       </c>
       <c r="G24" t="n">
-        <v>0.656</v>
+        <v>0.651</v>
       </c>
       <c r="H24" t="n">
         <v>48.2</v>
       </c>
       <c r="I24" t="n">
-        <v>41.3</v>
+        <v>41.1</v>
       </c>
       <c r="J24" t="n">
-        <v>83.59999999999999</v>
+        <v>83.5</v>
       </c>
       <c r="K24" t="n">
-        <v>0.494</v>
+        <v>0.492</v>
       </c>
       <c r="L24" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="M24" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="N24" t="n">
-        <v>0.382</v>
+        <v>0.383</v>
       </c>
       <c r="O24" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="P24" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.791</v>
+        <v>0.79</v>
       </c>
       <c r="R24" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>32.3</v>
+        <v>32.2</v>
       </c>
       <c r="T24" t="n">
-        <v>41</v>
+        <v>40.9</v>
       </c>
       <c r="U24" t="n">
-        <v>26.7</v>
+        <v>26.6</v>
       </c>
       <c r="V24" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="W24" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="X24" t="n">
         <v>6.8</v>
@@ -4731,34 +4798,34 @@
         <v>3.8</v>
       </c>
       <c r="Z24" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="AA24" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AB24" t="n">
-        <v>109.6</v>
+        <v>109.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AE24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AF24" t="n">
         <v>7</v>
       </c>
       <c r="AG24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH24" t="n">
         <v>20</v>
       </c>
       <c r="AI24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ24" t="n">
         <v>6</v>
@@ -4776,10 +4843,10 @@
         <v>4</v>
       </c>
       <c r="AO24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ24" t="n">
         <v>5</v>
@@ -4791,7 +4858,7 @@
         <v>6</v>
       </c>
       <c r="AT24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU24" t="n">
         <v>1</v>
@@ -4806,10 +4873,10 @@
         <v>2</v>
       </c>
       <c r="AY24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AZ24" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA24" t="n">
         <v>21</v>
@@ -4818,7 +4885,7 @@
         <v>2</v>
       </c>
       <c r="BC24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-11-2007-08</t>
+          <t>2008-03-11</t>
         </is>
       </c>
     </row>
@@ -4847,16 +4914,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E25" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F25" t="n">
         <v>31</v>
       </c>
       <c r="G25" t="n">
-        <v>0.523</v>
+        <v>0.516</v>
       </c>
       <c r="H25" t="n">
         <v>48.7</v>
@@ -4880,16 +4947,16 @@
         <v>0.372</v>
       </c>
       <c r="O25" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="P25" t="n">
         <v>23.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.766</v>
+        <v>0.765</v>
       </c>
       <c r="R25" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="S25" t="n">
         <v>29.8</v>
@@ -4913,22 +4980,22 @@
         <v>3.7</v>
       </c>
       <c r="Z25" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="AA25" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AB25" t="n">
-        <v>95.7</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="AC25" t="n">
-        <v>-0.7</v>
+        <v>-0.8</v>
       </c>
       <c r="AD25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF25" t="n">
         <v>15</v>
@@ -4949,7 +5016,7 @@
         <v>18</v>
       </c>
       <c r="AL25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM25" t="n">
         <v>16</v>
@@ -4961,7 +5028,7 @@
         <v>22</v>
       </c>
       <c r="AP25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ25" t="n">
         <v>12</v>
@@ -4970,7 +5037,7 @@
         <v>21</v>
       </c>
       <c r="AS25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT25" t="n">
         <v>26</v>
@@ -4985,7 +5052,7 @@
         <v>30</v>
       </c>
       <c r="AX25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY25" t="n">
         <v>1</v>
@@ -4994,7 +5061,7 @@
         <v>9</v>
       </c>
       <c r="BA25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BB25" t="n">
         <v>25</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-11-2007-08</t>
+          <t>2008-03-11</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>-2.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AE26" t="n">
         <v>18</v>
@@ -5119,7 +5186,7 @@
         <v>18</v>
       </c>
       <c r="AH26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI26" t="n">
         <v>15</v>
@@ -5137,7 +5204,7 @@
         <v>19</v>
       </c>
       <c r="AN26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO26" t="n">
         <v>2</v>
@@ -5158,7 +5225,7 @@
         <v>28</v>
       </c>
       <c r="AU26" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AV26" t="n">
         <v>29</v>
@@ -5182,7 +5249,7 @@
         <v>8</v>
       </c>
       <c r="BC26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-11-2007-08</t>
+          <t>2008-03-11</t>
         </is>
       </c>
     </row>
@@ -5289,16 +5356,16 @@
         <v>5</v>
       </c>
       <c r="AD27" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AE27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF27" t="n">
         <v>3</v>
       </c>
       <c r="AG27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH27" t="n">
         <v>24</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-11-2007-08</t>
+          <t>2008-03-11</t>
         </is>
       </c>
     </row>
@@ -5393,37 +5460,37 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E28" t="n">
         <v>16</v>
       </c>
       <c r="F28" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G28" t="n">
-        <v>0.25</v>
+        <v>0.254</v>
       </c>
       <c r="H28" t="n">
         <v>48.3</v>
       </c>
       <c r="I28" t="n">
-        <v>37.8</v>
+        <v>37.7</v>
       </c>
       <c r="J28" t="n">
         <v>84.90000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>0.445</v>
+        <v>0.444</v>
       </c>
       <c r="L28" t="n">
         <v>4</v>
       </c>
       <c r="M28" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="N28" t="n">
-        <v>0.34</v>
+        <v>0.337</v>
       </c>
       <c r="O28" t="n">
         <v>17.6</v>
@@ -5435,13 +5502,13 @@
         <v>0.768</v>
       </c>
       <c r="R28" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="S28" t="n">
         <v>33.4</v>
       </c>
       <c r="T28" t="n">
-        <v>45</v>
+        <v>45.2</v>
       </c>
       <c r="U28" t="n">
         <v>21.6</v>
@@ -5453,7 +5520,7 @@
         <v>6.4</v>
       </c>
       <c r="X28" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Y28" t="n">
         <v>5.4</v>
@@ -5465,13 +5532,13 @@
         <v>19.8</v>
       </c>
       <c r="AB28" t="n">
-        <v>97.2</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="AC28" t="n">
         <v>-7.7</v>
       </c>
       <c r="AD28" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AE28" t="n">
         <v>27</v>
@@ -5501,7 +5568,7 @@
         <v>29</v>
       </c>
       <c r="AN28" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AO28" t="n">
         <v>24</v>
@@ -5513,7 +5580,7 @@
         <v>11</v>
       </c>
       <c r="AR28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS28" t="n">
         <v>2</v>
@@ -5522,7 +5589,7 @@
         <v>1</v>
       </c>
       <c r="AU28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AV28" t="n">
         <v>30</v>
@@ -5537,7 +5604,7 @@
         <v>26</v>
       </c>
       <c r="AZ28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA28" t="n">
         <v>26</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-11-2007-08</t>
+          <t>2008-03-11</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E29" t="n">
         <v>34</v>
       </c>
       <c r="F29" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G29" t="n">
-        <v>0.54</v>
+        <v>0.548</v>
       </c>
       <c r="H29" t="n">
         <v>48.4</v>
@@ -5593,7 +5660,7 @@
         <v>38.1</v>
       </c>
       <c r="J29" t="n">
-        <v>81.8</v>
+        <v>81.7</v>
       </c>
       <c r="K29" t="n">
         <v>0.466</v>
@@ -5602,7 +5669,7 @@
         <v>7.5</v>
       </c>
       <c r="M29" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="N29" t="n">
         <v>0.406</v>
@@ -5614,7 +5681,7 @@
         <v>20.7</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="R29" t="n">
         <v>9.800000000000001</v>
@@ -5635,25 +5702,25 @@
         <v>7</v>
       </c>
       <c r="X29" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Y29" t="n">
         <v>4</v>
       </c>
       <c r="Z29" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AA29" t="n">
         <v>18.3</v>
       </c>
       <c r="AB29" t="n">
-        <v>100.5</v>
+        <v>100.4</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AD29" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="AE29" t="n">
         <v>14</v>
@@ -5665,7 +5732,7 @@
         <v>14</v>
       </c>
       <c r="AH29" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AI29" t="n">
         <v>7</v>
@@ -5719,7 +5786,7 @@
         <v>5</v>
       </c>
       <c r="AZ29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA29" t="n">
         <v>29</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-11-2007-08</t>
+          <t>2008-03-11</t>
         </is>
       </c>
     </row>
@@ -5757,28 +5824,28 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E30" t="n">
         <v>42</v>
       </c>
       <c r="F30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G30" t="n">
-        <v>0.646</v>
+        <v>0.656</v>
       </c>
       <c r="H30" t="n">
         <v>48.1</v>
       </c>
       <c r="I30" t="n">
-        <v>39.9</v>
+        <v>40</v>
       </c>
       <c r="J30" t="n">
-        <v>80.5</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>0.496</v>
+        <v>0.497</v>
       </c>
       <c r="L30" t="n">
         <v>4.6</v>
@@ -5787,34 +5854,34 @@
         <v>12.5</v>
       </c>
       <c r="N30" t="n">
-        <v>0.367</v>
+        <v>0.368</v>
       </c>
       <c r="O30" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="P30" t="n">
-        <v>28.8</v>
+        <v>28.6</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.754</v>
+        <v>0.756</v>
       </c>
       <c r="R30" t="n">
         <v>11.4</v>
       </c>
       <c r="S30" t="n">
-        <v>29.6</v>
+        <v>29.5</v>
       </c>
       <c r="T30" t="n">
-        <v>41</v>
+        <v>40.9</v>
       </c>
       <c r="U30" t="n">
-        <v>26.3</v>
+        <v>26.5</v>
       </c>
       <c r="V30" t="n">
         <v>15.1</v>
       </c>
       <c r="W30" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="X30" t="n">
         <v>4.3</v>
@@ -5823,28 +5890,28 @@
         <v>5.4</v>
       </c>
       <c r="Z30" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="AA30" t="n">
         <v>23.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>106.1</v>
+        <v>106.3</v>
       </c>
       <c r="AC30" t="n">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="AD30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE30" t="n">
         <v>6</v>
       </c>
       <c r="AF30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH30" t="n">
         <v>30</v>
@@ -5868,7 +5935,7 @@
         <v>12</v>
       </c>
       <c r="AO30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP30" t="n">
         <v>3</v>
@@ -5880,10 +5947,10 @@
         <v>16</v>
       </c>
       <c r="AS30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU30" t="n">
         <v>2</v>
@@ -5895,7 +5962,7 @@
         <v>3</v>
       </c>
       <c r="AX30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY30" t="n">
         <v>25</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-11-2007-08</t>
+          <t>2008-03-11</t>
         </is>
       </c>
     </row>
@@ -5939,37 +6006,37 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E31" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F31" t="n">
         <v>32</v>
       </c>
       <c r="G31" t="n">
-        <v>0.492</v>
+        <v>0.484</v>
       </c>
       <c r="H31" t="n">
         <v>48.6</v>
       </c>
       <c r="I31" t="n">
-        <v>36.2</v>
+        <v>36.1</v>
       </c>
       <c r="J31" t="n">
-        <v>82</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>0.442</v>
+        <v>0.441</v>
       </c>
       <c r="L31" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="M31" t="n">
-        <v>19.1</v>
+        <v>19.3</v>
       </c>
       <c r="N31" t="n">
-        <v>0.341</v>
+        <v>0.34</v>
       </c>
       <c r="O31" t="n">
         <v>19.3</v>
@@ -5978,7 +6045,7 @@
         <v>24.3</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.792</v>
+        <v>0.793</v>
       </c>
       <c r="R31" t="n">
         <v>12.4</v>
@@ -5987,19 +6054,19 @@
         <v>29.7</v>
       </c>
       <c r="T31" t="n">
-        <v>42</v>
+        <v>42.1</v>
       </c>
       <c r="U31" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="V31" t="n">
         <v>13.6</v>
       </c>
       <c r="W31" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="X31" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Y31" t="n">
         <v>4.3</v>
@@ -6011,13 +6078,13 @@
         <v>20.2</v>
       </c>
       <c r="AB31" t="n">
-        <v>98.2</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="AC31" t="n">
-        <v>-0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="AE31" t="n">
         <v>16</v>
@@ -6032,19 +6099,19 @@
         <v>2</v>
       </c>
       <c r="AI31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AK31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL31" t="n">
         <v>13</v>
       </c>
       <c r="AM31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AN31" t="n">
         <v>23</v>
@@ -6068,13 +6135,13 @@
         <v>15</v>
       </c>
       <c r="AU31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AV31" t="n">
         <v>8</v>
       </c>
       <c r="AW31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX31" t="n">
         <v>8</v>
@@ -6083,10 +6150,10 @@
         <v>7</v>
       </c>
       <c r="AZ31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB31" t="n">
         <v>15</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-11-2007-08</t>
+          <t>2008-03-11</t>
         </is>
       </c>
     </row>
